--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484561_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484561_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.3338</v>
+        <v>2.6024</v>
       </c>
       <c r="E2" t="n">
-        <v>2.7198</v>
+        <v>2.3352</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6141</v>
+        <v>0.2672</v>
       </c>
       <c r="G2" t="n">
         <v>2.6585</v>
@@ -610,13 +610,13 @@
         <v>2.3823</v>
       </c>
       <c r="S2" t="n">
-        <v>0.4475</v>
+        <v>-0.2839</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.07539999999999999</v>
+        <v>-0.46</v>
       </c>
       <c r="U2" t="n">
-        <v>0.5229</v>
+        <v>0.1761</v>
       </c>
       <c r="V2" t="n">
         <v>-0.3219</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.0901</v>
+        <v>1.0654</v>
       </c>
       <c r="E4" t="n">
         <v>0.215</v>
       </c>
       <c r="F4" t="n">
-        <v>0.8752</v>
+        <v>0.8504</v>
       </c>
       <c r="G4" t="n">
         <v>0.1352</v>
@@ -766,13 +766,13 @@
         <v>1.2828</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.0346</v>
+        <v>-0.0594</v>
       </c>
       <c r="T4" t="n">
         <v>-0.0558</v>
       </c>
       <c r="U4" t="n">
-        <v>0.0212</v>
+        <v>-0.0036</v>
       </c>
       <c r="V4" t="n">
         <v>0.6231</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.6067</v>
+        <v>0.9283</v>
       </c>
       <c r="E5" t="n">
-        <v>1.9431</v>
+        <v>2.1905</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.3365</v>
+        <v>-1.2621</v>
       </c>
       <c r="G5" t="n">
         <v>1.9494</v>
@@ -844,13 +844,13 @@
         <v>1.4661</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.2695</v>
+        <v>-0.9478</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.5875</v>
+        <v>-0.3401</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.6820000000000001</v>
+        <v>-0.6077</v>
       </c>
       <c r="V5" t="n">
         <v>-0.6231</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>S. DOMINGUEZ ALEIXANDRE</t>
+          <t>A. COMPANY LOPEZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.3306</v>
+        <v>0.8962</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.9497</v>
+        <v>-0.4658</v>
       </c>
       <c r="F6" t="n">
-        <v>1.2803</v>
+        <v>1.362</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.2836</v>
+        <v>2.0883</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.1554</v>
+        <v>-0.5691000000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.1282</v>
+        <v>2.6573</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.6194</v>
+        <v>1.4735</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0217</v>
+        <v>-1.152</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.641</v>
+        <v>2.6255</v>
       </c>
       <c r="M6" t="n">
-        <v>0.3357</v>
+        <v>0.6148</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.1771</v>
+        <v>0.583</v>
       </c>
       <c r="O6" t="n">
-        <v>0.5128</v>
+        <v>0.0318</v>
       </c>
       <c r="P6" t="n">
-        <v>0.733</v>
+        <v>-0.3665</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-1.8326</v>
       </c>
       <c r="R6" t="n">
-        <v>0.733</v>
+        <v>1.4661</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.1188</v>
+        <v>-0.5036</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.3303</v>
+        <v>-0.1067</v>
       </c>
       <c r="U6" t="n">
-        <v>0.2115</v>
+        <v>-0.3969</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>-0.3219</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-0.3219</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. COMPANY LOPEZ</t>
+          <t>S. DOMINGUEZ ALEIXANDRE</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.2365</v>
+        <v>0.3991</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.0016</v>
+        <v>-0.7574</v>
       </c>
       <c r="F7" t="n">
-        <v>1.2381</v>
+        <v>1.1564</v>
       </c>
       <c r="G7" t="n">
-        <v>2.0883</v>
+        <v>-0.2836</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.5691000000000001</v>
+        <v>-0.1554</v>
       </c>
       <c r="I7" t="n">
-        <v>2.6573</v>
+        <v>-0.1282</v>
       </c>
       <c r="J7" t="n">
-        <v>1.4735</v>
+        <v>-0.6194</v>
       </c>
       <c r="K7" t="n">
-        <v>-1.152</v>
+        <v>0.0217</v>
       </c>
       <c r="L7" t="n">
-        <v>2.6255</v>
+        <v>-0.641</v>
       </c>
       <c r="M7" t="n">
-        <v>0.6148</v>
+        <v>0.3357</v>
       </c>
       <c r="N7" t="n">
-        <v>0.583</v>
+        <v>-0.1771</v>
       </c>
       <c r="O7" t="n">
-        <v>0.0318</v>
+        <v>0.5128</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.3665</v>
+        <v>0.733</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.8326</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.4661</v>
+        <v>0.733</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.1633</v>
+        <v>-0.0503</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.6425</v>
+        <v>-0.138</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.5208</v>
+        <v>0.0877</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.3219</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.3219</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>D. GONZALEZ FERRER</t>
+          <t>A. GONZALEZ SOLER</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.234</v>
+        <v>-0.0919</v>
       </c>
       <c r="E8" t="n">
-        <v>1.5902</v>
+        <v>-0.8572</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.3562</v>
+        <v>0.7654</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.706</v>
+        <v>0.3525</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.3501</v>
+        <v>0.2564</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.356</v>
+        <v>0.0961</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.4234</v>
+        <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.5484</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>0.125</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.2827</v>
+        <v>0.3525</v>
       </c>
       <c r="N8" t="n">
-        <v>0.1983</v>
+        <v>0.2564</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.481</v>
+        <v>0.0961</v>
       </c>
       <c r="P8" t="n">
-        <v>0.733</v>
+        <v>0.3665</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0.733</v>
+        <v>0.3665</v>
       </c>
       <c r="S8" t="n">
-        <v>1.474</v>
+        <v>-0.1878</v>
       </c>
       <c r="T8" t="n">
-        <v>2.0136</v>
+        <v>-0.2342</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.5396</v>
+        <v>0.0464</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.267</v>
+        <v>-0.6231</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>-0.6231</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.267</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A. GONZALEZ SOLER</t>
+          <t>D. GONZALEZ FERRER</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.0394</v>
+        <v>-1.1255</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.9534</v>
+        <v>0.1068</v>
       </c>
       <c r="F9" t="n">
-        <v>0.914</v>
+        <v>-1.2323</v>
       </c>
       <c r="G9" t="n">
-        <v>0.3525</v>
+        <v>-0.706</v>
       </c>
       <c r="H9" t="n">
-        <v>0.2564</v>
+        <v>-0.3501</v>
       </c>
       <c r="I9" t="n">
-        <v>0.0961</v>
+        <v>-0.356</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>-0.4234</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>-0.5484</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>0.125</v>
       </c>
       <c r="M9" t="n">
-        <v>0.3525</v>
+        <v>-0.2827</v>
       </c>
       <c r="N9" t="n">
-        <v>0.2564</v>
+        <v>0.1983</v>
       </c>
       <c r="O9" t="n">
-        <v>0.0961</v>
+        <v>-0.481</v>
       </c>
       <c r="P9" t="n">
-        <v>0.3665</v>
+        <v>0.733</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>0.3665</v>
+        <v>0.733</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.1353</v>
+        <v>0.1144</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.3303</v>
+        <v>0.5302</v>
       </c>
       <c r="U9" t="n">
-        <v>0.195</v>
+        <v>-0.4157</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.6231</v>
+        <v>-1.267</v>
       </c>
       <c r="W9" t="n">
-        <v>-0.6231</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-1.267</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.7545</v>
+        <v>-1.2871</v>
       </c>
       <c r="E10" t="n">
-        <v>0.8943</v>
+        <v>1.2378</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.6488</v>
+        <v>-2.5249</v>
       </c>
       <c r="G10" t="n">
         <v>0.5167</v>
@@ -1234,13 +1234,13 @@
         <v>2.7489</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.6768</v>
+        <v>-1.2095</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.3031</v>
+        <v>-0.9596</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.3737</v>
+        <v>-0.2498</v>
       </c>
       <c r="V10" t="n">
         <v>0.3219</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.8835</v>
+        <v>-2.0233</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.6658</v>
+        <v>-2.9543</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7823</v>
+        <v>0.931</v>
       </c>
       <c r="G11" t="n">
         <v>0.8584000000000001</v>
@@ -1312,13 +1312,13 @@
         <v>1.0995</v>
       </c>
       <c r="S11" t="n">
-        <v>0.4468</v>
+        <v>0.3069</v>
       </c>
       <c r="T11" t="n">
-        <v>0.457</v>
+        <v>0.1686</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.0103</v>
+        <v>0.1384</v>
       </c>
       <c r="V11" t="n">
         <v>-0.6231</v>
@@ -1333,7 +1333,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>J. SOSA GONZALEZ</t>
+          <t>P. BUSTAMANTE CONTRERAS</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,73 +1345,73 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.5834</v>
+        <v>-3.1892</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.8895</v>
+        <v>-2.4739</v>
       </c>
       <c r="F12" t="n">
-        <v>0.3061</v>
+        <v>-0.7153</v>
       </c>
       <c r="G12" t="n">
-        <v>-1.9101</v>
+        <v>-4.3946</v>
       </c>
       <c r="H12" t="n">
-        <v>-1.0187</v>
+        <v>-1.6667</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.8914</v>
+        <v>-2.7279</v>
       </c>
       <c r="J12" t="n">
-        <v>0.435</v>
+        <v>-2.8358</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.3409</v>
+        <v>-1.0377</v>
       </c>
       <c r="L12" t="n">
-        <v>0.7759</v>
+        <v>-1.7981</v>
       </c>
       <c r="M12" t="n">
-        <v>-2.3451</v>
+        <v>-1.5588</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.6778</v>
+        <v>-0.629</v>
       </c>
       <c r="O12" t="n">
-        <v>-1.6673</v>
+        <v>-0.9298999999999999</v>
       </c>
       <c r="P12" t="n">
-        <v>-1.2828</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>-3.6651</v>
+        <v>-1.8326</v>
       </c>
       <c r="R12" t="n">
-        <v>2.3823</v>
+        <v>1.8326</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.4114</v>
+        <v>-0.7055</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.6802</v>
+        <v>-0.3499</v>
       </c>
       <c r="U12" t="n">
-        <v>0.2688</v>
+        <v>-0.3556</v>
       </c>
       <c r="V12" t="n">
-        <v>0.0208</v>
+        <v>1.9109</v>
       </c>
       <c r="W12" t="n">
-        <v>0.0208</v>
+        <v>2.5444</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>-0.6335</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>P. BUSTAMANTE CONTRERAS</t>
+          <t>J. SOSA GONZALEZ</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-3.7225</v>
+        <v>-3.7077</v>
       </c>
       <c r="E13" t="n">
-        <v>-2.8585</v>
+        <v>-3.6421</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.864</v>
+        <v>-0.0655</v>
       </c>
       <c r="G13" t="n">
-        <v>-4.3946</v>
+        <v>-1.9101</v>
       </c>
       <c r="H13" t="n">
-        <v>-1.6667</v>
+        <v>-1.0187</v>
       </c>
       <c r="I13" t="n">
-        <v>-2.7279</v>
+        <v>-0.8914</v>
       </c>
       <c r="J13" t="n">
-        <v>-2.8358</v>
+        <v>0.435</v>
       </c>
       <c r="K13" t="n">
-        <v>-1.0377</v>
+        <v>-0.3409</v>
       </c>
       <c r="L13" t="n">
-        <v>-1.7981</v>
+        <v>0.7759</v>
       </c>
       <c r="M13" t="n">
-        <v>-1.5588</v>
+        <v>-2.3451</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.629</v>
+        <v>-0.6778</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.9298999999999999</v>
+        <v>-1.6673</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>-1.2828</v>
       </c>
       <c r="Q13" t="n">
-        <v>-1.8326</v>
+        <v>-3.6651</v>
       </c>
       <c r="R13" t="n">
-        <v>1.8326</v>
+        <v>2.3823</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.2388</v>
+        <v>-0.5356</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.7345</v>
+        <v>-0.4329</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.5042</v>
+        <v>-0.1028</v>
       </c>
       <c r="V13" t="n">
-        <v>1.9109</v>
+        <v>0.0208</v>
       </c>
       <c r="W13" t="n">
-        <v>2.5444</v>
+        <v>0.0208</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.6335</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-4.5066</v>
+        <v>-3.8495</v>
       </c>
       <c r="E14" t="n">
-        <v>-1.5198</v>
+        <v>-1.1352</v>
       </c>
       <c r="F14" t="n">
-        <v>-2.9868</v>
+        <v>-2.7143</v>
       </c>
       <c r="G14" t="n">
         <v>-2.5202</v>
@@ -1546,13 +1546,13 @@
         <v>0.9163</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.0755</v>
+        <v>0.5816</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.129</v>
+        <v>0.2557</v>
       </c>
       <c r="U14" t="n">
-        <v>0.0535</v>
+        <v>0.326</v>
       </c>
       <c r="V14" t="n">
         <v>-1.9109</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-8.082899999999999</v>
+        <v>-7.807499999999999</v>
       </c>
       <c r="E15" t="n">
-        <v>-4.900599999999999</v>
+        <v>-4.6253</v>
       </c>
       <c r="F15" t="n">
-        <v>-3.1822</v>
+        <v>-3.182</v>
       </c>
       <c r="G15" t="n">
         <v>0.3198000000000008</v>
@@ -1597,7 +1597,7 @@
         <v>2.2427</v>
       </c>
       <c r="J15" t="n">
-        <v>9.687800000000001</v>
+        <v>9.687799999999999</v>
       </c>
       <c r="K15" t="n">
         <v>0.2299000000000002</v>
@@ -1624,13 +1624,13 @@
         <v>17.4094</v>
       </c>
       <c r="S15" t="n">
-        <v>-3.7557</v>
+        <v>-3.4805</v>
       </c>
       <c r="T15" t="n">
-        <v>-2.398</v>
+        <v>-2.1227</v>
       </c>
       <c r="U15" t="n">
-        <v>-1.3577</v>
+        <v>-1.3575</v>
       </c>
       <c r="V15" t="n">
         <v>-2.8143</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A. AZNAR MARTINEZ</t>
+          <t>K. MONTANO LINARES</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>7.7088</v>
+        <v>6.8538</v>
       </c>
       <c r="E16" t="n">
-        <v>4.7392</v>
+        <v>5.0879</v>
       </c>
       <c r="F16" t="n">
-        <v>2.9696</v>
+        <v>1.7659</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.4499</v>
+        <v>2.2904</v>
       </c>
       <c r="H16" t="n">
-        <v>-1.0782</v>
+        <v>1.5947</v>
       </c>
       <c r="I16" t="n">
-        <v>0.6283</v>
+        <v>0.6957</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.4069</v>
+        <v>5.1254</v>
       </c>
       <c r="K16" t="n">
-        <v>-1.0995</v>
+        <v>2.2817</v>
       </c>
       <c r="L16" t="n">
-        <v>0.6925</v>
+        <v>2.8437</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.043</v>
+        <v>-2.835</v>
       </c>
       <c r="N16" t="n">
-        <v>0.0213</v>
+        <v>-0.6870000000000001</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.0643</v>
+        <v>-2.148</v>
       </c>
       <c r="P16" t="n">
-        <v>2.0158</v>
+        <v>1.4661</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.1833</v>
+        <v>-2.0158</v>
       </c>
       <c r="R16" t="n">
-        <v>2.1991</v>
+        <v>3.4819</v>
       </c>
       <c r="S16" t="n">
-        <v>2.6639</v>
+        <v>0.5633</v>
       </c>
       <c r="T16" t="n">
-        <v>1.8296</v>
+        <v>-0.2545</v>
       </c>
       <c r="U16" t="n">
-        <v>0.8344</v>
+        <v>0.8178</v>
       </c>
       <c r="V16" t="n">
-        <v>3.479</v>
+        <v>2.5339</v>
       </c>
       <c r="W16" t="n">
-        <v>3.4998</v>
+        <v>2.2328</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.0208</v>
+        <v>0.3011</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>K. MONTANO LINARES</t>
+          <t>A. AZNAR MARTINEZ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>5.7524</v>
+        <v>6.3043</v>
       </c>
       <c r="E17" t="n">
-        <v>4.2225</v>
+        <v>3.6815</v>
       </c>
       <c r="F17" t="n">
-        <v>1.5299</v>
+        <v>2.6228</v>
       </c>
       <c r="G17" t="n">
-        <v>2.2904</v>
+        <v>-0.4499</v>
       </c>
       <c r="H17" t="n">
-        <v>1.5947</v>
+        <v>-1.0782</v>
       </c>
       <c r="I17" t="n">
-        <v>0.6957</v>
+        <v>0.6283</v>
       </c>
       <c r="J17" t="n">
-        <v>5.1254</v>
+        <v>-0.4069</v>
       </c>
       <c r="K17" t="n">
-        <v>2.2817</v>
+        <v>-1.0995</v>
       </c>
       <c r="L17" t="n">
-        <v>2.8437</v>
+        <v>0.6925</v>
       </c>
       <c r="M17" t="n">
-        <v>-2.835</v>
+        <v>-0.043</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.6870000000000001</v>
+        <v>0.0213</v>
       </c>
       <c r="O17" t="n">
-        <v>-2.148</v>
+        <v>-0.0643</v>
       </c>
       <c r="P17" t="n">
-        <v>1.4661</v>
+        <v>2.0158</v>
       </c>
       <c r="Q17" t="n">
-        <v>-2.0158</v>
+        <v>-0.1833</v>
       </c>
       <c r="R17" t="n">
-        <v>3.4819</v>
+        <v>2.1991</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.538</v>
+        <v>1.2594</v>
       </c>
       <c r="T17" t="n">
-        <v>-1.1199</v>
+        <v>0.7719</v>
       </c>
       <c r="U17" t="n">
-        <v>0.5819</v>
+        <v>0.4875</v>
       </c>
       <c r="V17" t="n">
-        <v>2.5339</v>
+        <v>3.479</v>
       </c>
       <c r="W17" t="n">
-        <v>2.2328</v>
+        <v>3.4998</v>
       </c>
       <c r="X17" t="n">
-        <v>0.3011</v>
+        <v>-0.0208</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.4768</v>
+        <v>2.2592</v>
       </c>
       <c r="E18" t="n">
-        <v>0.2839</v>
+        <v>0.7647</v>
       </c>
       <c r="F18" t="n">
-        <v>1.1929</v>
+        <v>1.4945</v>
       </c>
       <c r="G18" t="n">
         <v>2.8934</v>
@@ -1858,13 +1858,13 @@
         <v>3.1154</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.0684</v>
+        <v>0.714</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.1485</v>
+        <v>0.3322</v>
       </c>
       <c r="U18" t="n">
-        <v>0.0801</v>
+        <v>0.3818</v>
       </c>
       <c r="V18" t="n">
         <v>0.3011</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.7095</v>
+        <v>0.877</v>
       </c>
       <c r="E19" t="n">
-        <v>0.6516</v>
+        <v>0.8439</v>
       </c>
       <c r="F19" t="n">
-        <v>0.0579</v>
+        <v>0.0331</v>
       </c>
       <c r="G19" t="n">
         <v>0.4243</v>
@@ -1936,13 +1936,13 @@
         <v>0.1833</v>
       </c>
       <c r="S19" t="n">
-        <v>0.4239</v>
+        <v>0.5914</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.1101</v>
+        <v>0.0822</v>
       </c>
       <c r="U19" t="n">
-        <v>0.534</v>
+        <v>0.5092</v>
       </c>
       <c r="V19" t="n">
         <v>-0.3219</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A. MARTIN MARGARIT</t>
+          <t>P. ROCATI ALEGRE</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.321</v>
+        <v>0.3714</v>
       </c>
       <c r="E20" t="n">
-        <v>0.754</v>
+        <v>0.8046</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.433</v>
+        <v>-0.4332</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.8408</v>
+        <v>0.591</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.0521</v>
+        <v>0.6807</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.7886</v>
+        <v>-0.0897</v>
       </c>
       <c r="J20" t="n">
-        <v>0.9728</v>
+        <v>1.8596</v>
       </c>
       <c r="K20" t="n">
-        <v>0.2227</v>
+        <v>1.0837</v>
       </c>
       <c r="L20" t="n">
-        <v>0.7501</v>
+        <v>0.7759</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.8136</v>
+        <v>-1.2686</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.2748</v>
+        <v>-0.403</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.5388</v>
+        <v>-0.8656</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.3665</v>
+        <v>0.9163</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.8326</v>
+        <v>-1.0995</v>
       </c>
       <c r="R20" t="n">
-        <v>1.4661</v>
+        <v>2.0158</v>
       </c>
       <c r="S20" t="n">
-        <v>1.2167</v>
+        <v>0.4531</v>
       </c>
       <c r="T20" t="n">
-        <v>0.9698</v>
+        <v>0.0445</v>
       </c>
       <c r="U20" t="n">
-        <v>0.2469</v>
+        <v>0.4085</v>
       </c>
       <c r="V20" t="n">
-        <v>0.3115</v>
+        <v>-1.5889</v>
       </c>
       <c r="W20" t="n">
-        <v>0.6439</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.3324</v>
+        <v>-1.5889</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>P. ROCATI ALEGRE</t>
+          <t>A. MARTIN MARGARIT</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.4576</v>
+        <v>-0.2909</v>
       </c>
       <c r="E21" t="n">
-        <v>0.2277</v>
+        <v>-0.0153</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.6852</v>
+        <v>-0.2757</v>
       </c>
       <c r="G21" t="n">
-        <v>0.591</v>
+        <v>-0.8408</v>
       </c>
       <c r="H21" t="n">
-        <v>0.6807</v>
+        <v>-0.0521</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.0897</v>
+        <v>-0.7886</v>
       </c>
       <c r="J21" t="n">
-        <v>1.8596</v>
+        <v>0.9728</v>
       </c>
       <c r="K21" t="n">
-        <v>1.0837</v>
+        <v>0.2227</v>
       </c>
       <c r="L21" t="n">
-        <v>0.7759</v>
+        <v>0.7501</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.2686</v>
+        <v>-1.8136</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.403</v>
+        <v>-0.2748</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.8656</v>
+        <v>-1.5388</v>
       </c>
       <c r="P21" t="n">
-        <v>0.9163</v>
+        <v>-0.3665</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.0995</v>
+        <v>-1.8326</v>
       </c>
       <c r="R21" t="n">
-        <v>2.0158</v>
+        <v>1.4661</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.3759</v>
+        <v>0.6048</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.5324</v>
+        <v>0.2006</v>
       </c>
       <c r="U21" t="n">
-        <v>0.1565</v>
+        <v>0.4042</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.5889</v>
+        <v>0.3115</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>0.6439</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.5889</v>
+        <v>-0.3324</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>D. TOKAEV TOKAEV</t>
+          <t>A. MORAL SANMARTIN</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.09</v>
+        <v>-0.6188</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.9909</v>
+        <v>0.18</v>
       </c>
       <c r="F22" t="n">
-        <v>1.901</v>
+        <v>-0.7988</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.2932</v>
+        <v>-0.701</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.2675</v>
+        <v>-0.1789</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.0258</v>
+        <v>-0.5221</v>
       </c>
       <c r="J22" t="n">
-        <v>-1.0287</v>
+        <v>-0.0153</v>
       </c>
       <c r="K22" t="n">
-        <v>-1.1954</v>
+        <v>-0.1024</v>
       </c>
       <c r="L22" t="n">
-        <v>0.1667</v>
+        <v>0.0871</v>
       </c>
       <c r="M22" t="n">
-        <v>0.7354000000000001</v>
+        <v>-0.6857</v>
       </c>
       <c r="N22" t="n">
-        <v>0.9278999999999999</v>
+        <v>-0.0765</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.1925</v>
+        <v>-0.6092</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.9163</v>
+        <v>0.1833</v>
       </c>
       <c r="Q22" t="n">
         <v>-1.8326</v>
       </c>
       <c r="R22" t="n">
-        <v>0.9163</v>
+        <v>2.0158</v>
       </c>
       <c r="S22" t="n">
-        <v>0.1195</v>
+        <v>-0.1011</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.1297</v>
+        <v>-0.1945</v>
       </c>
       <c r="U22" t="n">
-        <v>0.2492</v>
+        <v>0.0935</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>2.2224</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>-2.2224</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A. MORAL SANMARTIN</t>
+          <t>D. TOKAEV TOKAEV</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.1666</v>
+        <v>-0.7651</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.0123</v>
+        <v>-2.7986</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.1543</v>
+        <v>2.0335</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.701</v>
+        <v>-0.2932</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.1789</v>
+        <v>-0.2675</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.5221</v>
+        <v>-0.0258</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.0153</v>
+        <v>-1.0287</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.1024</v>
+        <v>-1.1954</v>
       </c>
       <c r="L23" t="n">
-        <v>0.0871</v>
+        <v>0.1667</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.6857</v>
+        <v>0.7354000000000001</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.0765</v>
+        <v>0.9278999999999999</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.6092</v>
+        <v>-0.1925</v>
       </c>
       <c r="P23" t="n">
-        <v>0.1833</v>
+        <v>-0.9163</v>
       </c>
       <c r="Q23" t="n">
         <v>-1.8326</v>
       </c>
       <c r="R23" t="n">
-        <v>2.0158</v>
+        <v>0.9163</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.6489</v>
+        <v>0.4444</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.3869</v>
+        <v>0.0626</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.262</v>
+        <v>0.3818</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>2.2224</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-2.2224</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>J. MATE SEBASTIA</t>
+          <t>J. BALLESTER FERRANDIS</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,73 +2281,73 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-2.4299</v>
+        <v>-1.6577</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.6729</v>
+        <v>-1.5398</v>
       </c>
       <c r="F24" t="n">
-        <v>0.2429</v>
+        <v>-0.1179</v>
       </c>
       <c r="G24" t="n">
-        <v>-4.0861</v>
+        <v>-0.1479</v>
       </c>
       <c r="H24" t="n">
-        <v>-1.8166</v>
+        <v>0.2237</v>
       </c>
       <c r="I24" t="n">
-        <v>-2.2695</v>
+        <v>-0.3716</v>
       </c>
       <c r="J24" t="n">
-        <v>-1.3321</v>
+        <v>-0.4987</v>
       </c>
       <c r="K24" t="n">
-        <v>-1.0502</v>
+        <v>-0.576</v>
       </c>
       <c r="L24" t="n">
-        <v>-0.2819</v>
+        <v>0.07729999999999999</v>
       </c>
       <c r="M24" t="n">
-        <v>-2.754</v>
+        <v>0.3508</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.7664</v>
+        <v>0.7997</v>
       </c>
       <c r="O24" t="n">
-        <v>-1.9876</v>
+        <v>-0.4489</v>
       </c>
       <c r="P24" t="n">
-        <v>0.1833</v>
+        <v>-0.1833</v>
       </c>
       <c r="Q24" t="n">
-        <v>-2.9321</v>
+        <v>-0.9163</v>
       </c>
       <c r="R24" t="n">
-        <v>3.1154</v>
+        <v>0.733</v>
       </c>
       <c r="S24" t="n">
-        <v>2.1063</v>
+        <v>-0.0596</v>
       </c>
       <c r="T24" t="n">
-        <v>1.5913</v>
+        <v>-0.1248</v>
       </c>
       <c r="U24" t="n">
-        <v>0.5151</v>
+        <v>0.06519999999999999</v>
       </c>
       <c r="V24" t="n">
-        <v>-0.6335</v>
+        <v>-1.267</v>
       </c>
       <c r="W24" t="n">
         <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>-0.6335</v>
+        <v>-1.267</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>J. BALLESTER FERRANDIS</t>
+          <t>J. MATE SEBASTIA</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-2.7417</v>
+        <v>-3.3274</v>
       </c>
       <c r="E25" t="n">
-        <v>-2.0206</v>
+        <v>-3.8267</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.7211</v>
+        <v>0.4994</v>
       </c>
       <c r="G25" t="n">
-        <v>-0.1479</v>
+        <v>-4.0861</v>
       </c>
       <c r="H25" t="n">
-        <v>0.2237</v>
+        <v>-1.8166</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.3716</v>
+        <v>-2.2695</v>
       </c>
       <c r="J25" t="n">
-        <v>-0.4987</v>
+        <v>-1.3321</v>
       </c>
       <c r="K25" t="n">
-        <v>-0.576</v>
+        <v>-1.0502</v>
       </c>
       <c r="L25" t="n">
-        <v>0.07729999999999999</v>
+        <v>-0.2819</v>
       </c>
       <c r="M25" t="n">
-        <v>0.3508</v>
+        <v>-2.754</v>
       </c>
       <c r="N25" t="n">
-        <v>0.7997</v>
+        <v>-0.7664</v>
       </c>
       <c r="O25" t="n">
-        <v>-0.4489</v>
+        <v>-1.9876</v>
       </c>
       <c r="P25" t="n">
-        <v>-0.1833</v>
+        <v>0.1833</v>
       </c>
       <c r="Q25" t="n">
-        <v>-0.9163</v>
+        <v>-2.9321</v>
       </c>
       <c r="R25" t="n">
-        <v>0.733</v>
+        <v>3.1154</v>
       </c>
       <c r="S25" t="n">
-        <v>-1.1436</v>
+        <v>1.2089</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.6056</v>
+        <v>0.4374</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.538</v>
+        <v>0.7715</v>
       </c>
       <c r="V25" t="n">
-        <v>-1.267</v>
+        <v>-0.6335</v>
       </c>
       <c r="W25" t="n">
         <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>-1.267</v>
+        <v>-0.6335</v>
       </c>
     </row>
     <row r="26">
@@ -2437,16 +2437,16 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>8.082700000000001</v>
+        <v>10.0058</v>
       </c>
       <c r="E26" t="n">
         <v>3.1822</v>
       </c>
       <c r="F26" t="n">
-        <v>4.900599999999999</v>
+        <v>6.8236</v>
       </c>
       <c r="G26" t="n">
-        <v>-0.3197999999999991</v>
+        <v>-0.319799999999999</v>
       </c>
       <c r="H26" t="n">
         <v>1.9231</v>
@@ -2482,13 +2482,13 @@
         <v>19.2421</v>
       </c>
       <c r="S26" t="n">
-        <v>3.7555</v>
+        <v>5.678600000000001</v>
       </c>
       <c r="T26" t="n">
         <v>1.3576</v>
       </c>
       <c r="U26" t="n">
-        <v>2.3981</v>
+        <v>4.321</v>
       </c>
       <c r="V26" t="n">
         <v>2.8142</v>
